--- a/app/src/test/resources/bills/wechat_sample.xlsx
+++ b/app/src/test/resources/bills/wechat_sample.xlsx
@@ -19,7 +19,7 @@
     <t>微信支付账单明细</t>
   </si>
   <si>
-    <t>微信昵称：[ε=hv]</t>
+    <t>微信昵称：[测试用户]</t>
   </si>
   <si>
     <t>起始时间：[2026-08-28 00:00:00] 终止时间：[2026-09-28 23:48:49]</t>
@@ -97,10 +97,10 @@
     <t>扫二维码付款</t>
   </si>
   <si>
-    <t>涵玉小商店</t>
-  </si>
-  <si>
-    <t>收款方备注:二维码收款</t>
+    <t>示例收款人癸</t>
+  </si>
+  <si>
+    <t>示例商品</t>
   </si>
   <si>
     <t>支出</t>
@@ -112,10 +112,10 @@
     <t>已转账</t>
   </si>
   <si>
-    <t>53110002239126202609280066283958</t>
-  </si>
-  <si>
-    <t>10001073012026092801936006285567</t>
+    <t>00000000000000000000000000000019</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100019</t>
   </si>
   <si>
     <t>/</t>
@@ -124,46 +124,46 @@
     <t>商户消费</t>
   </si>
   <si>
-    <t>美团</t>
-  </si>
-  <si>
-    <t>美味基（百色新环球龙景店）-美团App-26092811200700001308112141190729</t>
+    <t>示例收款人甲</t>
+  </si>
+  <si>
+    <t>示例商品</t>
   </si>
   <si>
     <t>支付成功</t>
   </si>
   <si>
-    <t>4500000428202609281761889560</t>
-  </si>
-  <si>
-    <t>20260928124337U18054652232957131</t>
-  </si>
-  <si>
-    <t>铁塔能源有限公司</t>
-  </si>
-  <si>
-    <t>铁塔充电-小程序余额充值1.60元</t>
-  </si>
-  <si>
-    <t>4500000478202609275989025969</t>
-  </si>
-  <si>
-    <t>CDF20260927341339460</t>
-  </si>
-  <si>
-    <t>刘涵 (啊)</t>
-  </si>
-  <si>
-    <t>53110002229184202609270659388164</t>
-  </si>
-  <si>
-    <t>10001073012026092701494426152606</t>
+    <t>0000000000000000000000000020</t>
+  </si>
+  <si>
+    <t>00000000100020U18054652232957131</t>
+  </si>
+  <si>
+    <t>示例收款人乙</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000021</t>
+  </si>
+  <si>
+    <t>CDF00000000000100021</t>
+  </si>
+  <si>
+    <t>示例收款人丙</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000022</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100022</t>
   </si>
   <si>
     <t>二维码收款</t>
   </si>
   <si>
-    <t>嘻嘻 (果果)</t>
+    <t>示例收款人丁</t>
   </si>
   <si>
     <t>收入</t>
@@ -175,121 +175,121 @@
     <t>已收钱</t>
   </si>
   <si>
-    <t>10001073012026092701970832547567</t>
-  </si>
-  <si>
-    <t>53110002338234202609274158326008</t>
-  </si>
-  <si>
-    <t>10001073012026092701806928140531</t>
-  </si>
-  <si>
-    <t>百色市右江区果琪零食店（个体工商户）</t>
-  </si>
-  <si>
-    <t>恰货铺子广西百色右江福州街店</t>
-  </si>
-  <si>
-    <t>4200003153202609268963956497</t>
-  </si>
-  <si>
-    <t>7895084147098075</t>
-  </si>
-  <si>
-    <t>风声水起</t>
-  </si>
-  <si>
-    <t>4500000480202609268024046889</t>
-  </si>
-  <si>
-    <t>10069035114117904110050117082600</t>
-  </si>
-  <si>
-    <t>开心就好</t>
-  </si>
-  <si>
-    <t>53110002253107202609262322636408</t>
-  </si>
-  <si>
-    <t>10001073012026092601099650584586</t>
-  </si>
-  <si>
-    <t>肉类</t>
-  </si>
-  <si>
-    <t>4500000493202609265697658105</t>
-  </si>
-  <si>
-    <t>10069029220317904049150175970301</t>
-  </si>
-  <si>
-    <t>京东</t>
-  </si>
-  <si>
-    <t>京东-订单编号3633420015440509</t>
-  </si>
-  <si>
-    <t>4500000476202609263933419622</t>
-  </si>
-  <si>
-    <t>1012745726092612350300601</t>
+    <t>00000000000000000000000000000023</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000024</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100024</t>
+  </si>
+  <si>
+    <t>示例收款人戊</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000025</t>
+  </si>
+  <si>
+    <t>0000000000100025</t>
+  </si>
+  <si>
+    <t>示例收款人己</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000026</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100026</t>
+  </si>
+  <si>
+    <t>示例收款人庚</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000027</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100027</t>
+  </si>
+  <si>
+    <t>示例收款人辛</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000028</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100028</t>
+  </si>
+  <si>
+    <t>示例收款人壬</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000029</t>
+  </si>
+  <si>
+    <t>0000000000000000000100029</t>
   </si>
   <si>
     <t>转账</t>
   </si>
   <si>
-    <t>泉到.订水 30块钱押金 (财院.订水)</t>
-  </si>
-  <si>
-    <t>转账备注:微信转账</t>
+    <t>示例收款人癸</t>
+  </si>
+  <si>
+    <t>示例商品</t>
   </si>
   <si>
     <t>对方已收钱</t>
   </si>
   <si>
-    <t>53010003392054202609250532717950</t>
-  </si>
-  <si>
-    <t>1000050001202609250132424588363</t>
-  </si>
-  <si>
-    <t>韦佳志 (志哥)</t>
+    <t>00000000000000000000000000000030</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000100030</t>
+  </si>
+  <si>
+    <t>示例收款人甲</t>
   </si>
   <si>
     <t>已转入零钱通</t>
   </si>
   <si>
-    <t>1000050001202609250134156549632</t>
-  </si>
-  <si>
-    <t>4200003235202609243706487430</t>
-  </si>
-  <si>
-    <t>7895215961325580</t>
-  </si>
-  <si>
-    <t>中国电信</t>
-  </si>
-  <si>
-    <t>为191****4010充值30.0元，谨防诈骗</t>
-  </si>
-  <si>
-    <t>4500000468202609246013973458</t>
-  </si>
-  <si>
-    <t>ZY2609241524290083354065</t>
-  </si>
-  <si>
-    <t>黄祥富 (A.一航)</t>
-  </si>
-  <si>
-    <t>1000050001202609240537144472363</t>
-  </si>
-  <si>
-    <t>老爸 (爱不后悔)</t>
-  </si>
-  <si>
-    <t>1000050001202609240530089010793</t>
+    <t>0000000000000000000000000000031</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000032</t>
+  </si>
+  <si>
+    <t>0000000000100032</t>
+  </si>
+  <si>
+    <t>示例收款人乙</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000033</t>
+  </si>
+  <si>
+    <t>ZY0000000000000000100033</t>
+  </si>
+  <si>
+    <t>示例收款人丙</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000034</t>
+  </si>
+  <si>
+    <t>示例收款人丁</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000035</t>
   </si>
   <si>
     <t>转账-退款</t>
@@ -298,1060 +298,1060 @@
     <t>已全额退款</t>
   </si>
   <si>
-    <t>132100005020103202609240011587411726101</t>
-  </si>
-  <si>
-    <t>宋运开</t>
-  </si>
-  <si>
-    <t>53110002333067202609242962294359</t>
-  </si>
-  <si>
-    <t>10001073012026092401570807010642</t>
-  </si>
-  <si>
-    <t>百色市右江区李翔卤菜</t>
-  </si>
-  <si>
-    <t>小程序收银台订单</t>
-  </si>
-  <si>
-    <t>4500000465202609248774151902</t>
-  </si>
-  <si>
-    <t>20260924Nf0000000002003300030630</t>
-  </si>
-  <si>
-    <t>高哥夜市</t>
-  </si>
-  <si>
-    <t>53110002304114202609242501260403</t>
-  </si>
-  <si>
-    <t>10001073012026092401833569121608</t>
-  </si>
-  <si>
-    <t>校园折扣超市</t>
-  </si>
-  <si>
-    <t>普通订单</t>
-  </si>
-  <si>
-    <t>4200003244202609238659058942</t>
-  </si>
-  <si>
-    <t>481178137359131358003271</t>
-  </si>
-  <si>
-    <t>1000050001202609230537386945523</t>
-  </si>
-  <si>
-    <t>拼多多</t>
-  </si>
-  <si>
-    <t>商户单号XP1926092315100124154710001285</t>
-  </si>
-  <si>
-    <t>4500000450202609235721657047</t>
-  </si>
-  <si>
-    <t>XP1926092315100124154710001285</t>
-  </si>
-  <si>
-    <t>苍盾</t>
-  </si>
-  <si>
-    <t>用户付款</t>
-  </si>
-  <si>
-    <t>4500000446202609234984647670</t>
-  </si>
-  <si>
-    <t>E120260923144339C16602A16647U6CF</t>
-  </si>
-  <si>
-    <t>53110002235089202609230475098240</t>
-  </si>
-  <si>
-    <t>10001073012026092301435865093530</t>
-  </si>
-  <si>
-    <t>53110002313252202609230427275743</t>
-  </si>
-  <si>
-    <t>10001073012026092301158341570623</t>
-  </si>
-  <si>
-    <t>53010003405113202609230308446946</t>
-  </si>
-  <si>
-    <t>1000050001202609230134481745613</t>
-  </si>
-  <si>
-    <t>53110002297189202609230586356439</t>
-  </si>
-  <si>
-    <t>10001073012026092301661532019521</t>
-  </si>
-  <si>
-    <t>故里归长安</t>
-  </si>
-  <si>
-    <t>53110002257004202609232151518998</t>
-  </si>
-  <si>
-    <t>10001073012026092301530486481513</t>
-  </si>
-  <si>
-    <t>南宁市石墨肠粉</t>
-  </si>
-  <si>
-    <t>南宁市秀灵达心石磨肠粉店扫码收款</t>
-  </si>
-  <si>
-    <t>4500000464202609231066461869</t>
-  </si>
-  <si>
-    <t>20260923110113130266225071584517</t>
-  </si>
-  <si>
-    <t>53110002287174202609231211115570</t>
-  </si>
-  <si>
-    <t>10001073012026092301288695514546</t>
-  </si>
-  <si>
-    <t>53110002256134202609234176104719</t>
-  </si>
-  <si>
-    <t>10001073012026092301797662645506</t>
-  </si>
-  <si>
-    <t>53110002261022202609232818374062</t>
-  </si>
-  <si>
-    <t>10001073012026092301624329917630</t>
-  </si>
-  <si>
-    <t>53110002268060202609233084143132</t>
-  </si>
-  <si>
-    <t>10001073012026092301658114149575</t>
-  </si>
-  <si>
-    <t>53110002316131202609232825898236</t>
-  </si>
-  <si>
-    <t>10001073012026092301117572821560</t>
-  </si>
-  <si>
-    <t>53110002288154202609232296004555</t>
-  </si>
-  <si>
-    <t>10001073012026092301769231066601</t>
-  </si>
-  <si>
-    <t>53110002262147202609230881559969</t>
-  </si>
-  <si>
-    <t>10001073012026092301187019325506</t>
-  </si>
-  <si>
-    <t>53110002255103202609233409759751</t>
-  </si>
-  <si>
-    <t>10001073012026092301555220118539</t>
-  </si>
-  <si>
-    <t>53110002295221202609233896704494</t>
-  </si>
-  <si>
-    <t>10001073012026092301756925926545</t>
-  </si>
-  <si>
-    <t>53110002333055202609231437731476</t>
-  </si>
-  <si>
-    <t>10001073012026092301086852821637</t>
-  </si>
-  <si>
-    <t>53110002268124202609232796024334</t>
-  </si>
-  <si>
-    <t>10001073012026092301590892287525</t>
-  </si>
-  <si>
-    <t>1000050001202609230033312204953</t>
-  </si>
-  <si>
-    <t>53110002254162202609232099745886</t>
-  </si>
-  <si>
-    <t>10001073012026092301109801317540</t>
-  </si>
-  <si>
-    <t>广西财经学院</t>
-  </si>
-  <si>
-    <t>微信刷卡支付</t>
-  </si>
-  <si>
-    <t>4200003150202609221649066666</t>
-  </si>
-  <si>
-    <t>200005553108200592385643632991</t>
-  </si>
-  <si>
-    <t>4200003154202609229735211027</t>
-  </si>
-  <si>
-    <t>200005553107800538113160745110</t>
-  </si>
-  <si>
-    <t>1000050001202609210135873035332</t>
-  </si>
-  <si>
-    <t>南宁市西乡塘区百速杰便利店（个体工商户）</t>
-  </si>
-  <si>
-    <t>恰货铺子广西南宁西乡塘秀灵路东四里店</t>
-  </si>
-  <si>
-    <t>4200003150202609210076149698</t>
-  </si>
-  <si>
-    <t>7895215421444564</t>
-  </si>
-  <si>
-    <t>4200003144202609217467920009</t>
-  </si>
-  <si>
-    <t>200005553106447528961954110805</t>
-  </si>
-  <si>
-    <t>4200003154202609212043603621</t>
-  </si>
-  <si>
-    <t>200005553106423312384504272073</t>
-  </si>
-  <si>
-    <t>4200003154202609211752150396</t>
-  </si>
-  <si>
-    <t>200005553102028048384222563355</t>
-  </si>
-  <si>
-    <t>郑春朗 (. z Z)</t>
-  </si>
-  <si>
-    <t>53010003354233202609204045892060</t>
-  </si>
-  <si>
-    <t>1000050001202609200531831085785</t>
-  </si>
-  <si>
-    <t>潮匯隆江猪脚饭（正恒国际直营店）-美团App-26092011200700001306853259397729</t>
-  </si>
-  <si>
-    <t>4500000433202609201942480148</t>
-  </si>
-  <si>
-    <t>20260920191848U21621006009367661</t>
-  </si>
-  <si>
-    <t>抖音生活服务商家</t>
-  </si>
-  <si>
-    <t>可外卖芋圆葡萄秋季畅饮</t>
-  </si>
-  <si>
-    <t>4500000434202609202530281832</t>
-  </si>
-  <si>
-    <t>2001052609200705119951964771</t>
-  </si>
-  <si>
-    <t>秋菊</t>
-  </si>
-  <si>
-    <t>4500000473202609209911142753</t>
-  </si>
-  <si>
-    <t>10069192417617898864720177517400</t>
-  </si>
-  <si>
-    <t>中铁网络</t>
-  </si>
-  <si>
-    <t>12306消费</t>
-  </si>
-  <si>
-    <t>4500000428202609197670728374</t>
-  </si>
-  <si>
-    <t>M20260919259665743</t>
-  </si>
-  <si>
-    <t>百盛超市.</t>
-  </si>
-  <si>
-    <t>百盛超市(百盛超市)</t>
-  </si>
-  <si>
-    <t>4200003234202609194180856490</t>
-  </si>
-  <si>
-    <t>83620260919319212320</t>
-  </si>
-  <si>
-    <t>欢乐购</t>
-  </si>
-  <si>
-    <t>欢乐购平安路店</t>
-  </si>
-  <si>
-    <t>4200003142202609195094027441</t>
-  </si>
-  <si>
-    <t>7880011789809713000488</t>
-  </si>
-  <si>
-    <t>4200003160202609192133730474</t>
-  </si>
-  <si>
-    <t>83620260919678773275</t>
-  </si>
-  <si>
-    <t>雨中的福蓉花</t>
-  </si>
-  <si>
-    <t>4500000433202609195757057223</t>
-  </si>
-  <si>
-    <t>10069203349417897868940116069601</t>
-  </si>
-  <si>
-    <t>黑豹</t>
-  </si>
-  <si>
-    <t>53110002114166202609193479820321</t>
-  </si>
-  <si>
-    <t>10001073012026091901214103984516</t>
-  </si>
-  <si>
-    <t>王艳</t>
-  </si>
-  <si>
-    <t>53110002122071202609191496169776</t>
-  </si>
-  <si>
-    <t>10001073012026091901707354016565</t>
-  </si>
-  <si>
-    <t>4200003228202609180379418666</t>
-  </si>
-  <si>
-    <t>7895084411049884</t>
-  </si>
-  <si>
-    <t>顶天立地</t>
-  </si>
-  <si>
-    <t>53110002280148202609183936021896</t>
-  </si>
-  <si>
-    <t>10001073012026091801547918695500</t>
-  </si>
-  <si>
-    <t>宇翔渔具店</t>
-  </si>
-  <si>
-    <t>动态码牌交易</t>
-  </si>
-  <si>
-    <t>4200003141202609186359589228</t>
-  </si>
-  <si>
-    <t>20260918181513R2436719</t>
-  </si>
-  <si>
-    <t>黄记铁匠（刀具）</t>
-  </si>
-  <si>
-    <t>53110002125020202609172935231590</t>
-  </si>
-  <si>
-    <t>10001073012026091701664563335506</t>
-  </si>
-  <si>
-    <t>德哥18778680140</t>
-  </si>
-  <si>
-    <t>53110002119065202609170957918789</t>
-  </si>
-  <si>
-    <t>10001073012026091701489789939567</t>
-  </si>
-  <si>
-    <t>广西国际博览事务局</t>
-  </si>
-  <si>
-    <t>公众开放日购票</t>
-  </si>
-  <si>
-    <t>4500000442202609172972816143</t>
-  </si>
-  <si>
-    <t>1003502026091717180500130823</t>
-  </si>
-  <si>
-    <t>4500000435202609172151700687</t>
-  </si>
-  <si>
-    <t>1003502026091717145700130789</t>
-  </si>
-  <si>
-    <t>4500000450202609177236361211</t>
-  </si>
-  <si>
-    <t>1003502026091716412900130438</t>
-  </si>
-  <si>
-    <t>4500000449202609173864134383</t>
-  </si>
-  <si>
-    <t>1003502026091716380300130401</t>
-  </si>
-  <si>
-    <t>百色市右江区美佳乐超市</t>
-  </si>
-  <si>
-    <t>百色市右江区美佳乐超市(美佳乐超市总部)</t>
-  </si>
-  <si>
-    <t>4200003240202609160406094186</t>
-  </si>
-  <si>
-    <t>5811988133260916</t>
-  </si>
-  <si>
-    <t>4200003237202609162026383165</t>
-  </si>
-  <si>
-    <t>200005553104300365825924532254</t>
-  </si>
-  <si>
-    <t>南宁市自己家优选果品批发</t>
-  </si>
-  <si>
-    <t>4500000452202609157343563771</t>
-  </si>
-  <si>
-    <t>20260915CCc7a0ff</t>
-  </si>
-  <si>
-    <t>无可乐纯享双辣堡+半鸡可配送</t>
-  </si>
-  <si>
-    <t>4500000455202609159786594659</t>
-  </si>
-  <si>
-    <t>2001052609150105002457713303</t>
-  </si>
-  <si>
-    <t>4200003241202609157259709539</t>
-  </si>
-  <si>
-    <t>200005553103723676673948274124</t>
-  </si>
-  <si>
-    <t>校园网 (W)</t>
-  </si>
-  <si>
-    <t>1000050001202609140539824984956</t>
-  </si>
-  <si>
-    <t>4200003244202609143473089501</t>
-  </si>
-  <si>
-    <t>200005553109939856385898785813</t>
-  </si>
-  <si>
-    <t>蒙宏略 (OK)</t>
-  </si>
-  <si>
-    <t>1000050001202609130732093404483</t>
-  </si>
-  <si>
-    <t>1000050001202609130431467928351</t>
-  </si>
-  <si>
-    <t>李倬林 (安笙)</t>
-  </si>
-  <si>
-    <t>1000050001202609140223909987881</t>
-  </si>
-  <si>
-    <t>唐丰旺 (韫)</t>
-  </si>
-  <si>
-    <t>1000050001202609130436928794727</t>
-  </si>
-  <si>
-    <t>1000050001202609130236070059340</t>
-  </si>
-  <si>
-    <t>1000050001202609130638809453431</t>
-  </si>
-  <si>
-    <t>杨成龙 (Clong)</t>
-  </si>
-  <si>
-    <t>1000050001202609130432941050320</t>
-  </si>
-  <si>
-    <t>4200003232202609143374288478</t>
-  </si>
-  <si>
-    <t>200005553107639898113179870685</t>
-  </si>
-  <si>
-    <t>京东-订单编号3620420007945336</t>
-  </si>
-  <si>
-    <t>4500000367202609139705855085</t>
-  </si>
-  <si>
-    <t>1012742126091320015206305</t>
-  </si>
-  <si>
-    <t>新店开业丨新会员100网费</t>
-  </si>
-  <si>
-    <t>4500000328202609136319791099</t>
-  </si>
-  <si>
-    <t>2001052609130705243607073917</t>
-  </si>
-  <si>
-    <t>53010003373077202609132509849196</t>
-  </si>
-  <si>
-    <t>1000050001202609130035331758506</t>
-  </si>
-  <si>
-    <t>4500000380202609135121670955</t>
-  </si>
-  <si>
-    <t>M20260913203004890</t>
-  </si>
-  <si>
-    <t>4200003236202609133501605263</t>
-  </si>
-  <si>
-    <t>200005553103421505536048497836</t>
-  </si>
-  <si>
-    <t>4200003235202609120896447918</t>
-  </si>
-  <si>
-    <t>200005553102098876416962405023</t>
-  </si>
-  <si>
-    <t>4200003144202609121514054358</t>
-  </si>
-  <si>
-    <t>200005553107235772416556331693</t>
-  </si>
-  <si>
-    <t>4200003153202609125811636078</t>
-  </si>
-  <si>
-    <t>200005553105627720704648995031</t>
-  </si>
-  <si>
-    <t>财院水果文印店丨南宁店</t>
-  </si>
-  <si>
-    <t>53110002107147202609112845312018</t>
-  </si>
-  <si>
-    <t>10001073012026091101977705901587</t>
-  </si>
-  <si>
-    <t>4200003241202609110967241684</t>
-  </si>
-  <si>
-    <t>200005553103499092993088231458</t>
-  </si>
-  <si>
-    <t>4200003145202609114086039117</t>
-  </si>
-  <si>
-    <t>200005553108448919553919776273</t>
-  </si>
-  <si>
-    <t>4200003148202609111618706292</t>
-  </si>
-  <si>
-    <t>200005553106669268992026996753</t>
-  </si>
-  <si>
-    <t>4200003148202609107927749123</t>
-  </si>
-  <si>
-    <t>200005553105380363265122935943</t>
-  </si>
-  <si>
-    <t>53010003397217202609100200616533</t>
-  </si>
-  <si>
-    <t>1000050001202609100634526495421</t>
-  </si>
-  <si>
-    <t>4200003228202609105809728334</t>
-  </si>
-  <si>
-    <t>200005553108236579841303552545</t>
-  </si>
-  <si>
-    <t>4200003231202609098259783082</t>
-  </si>
-  <si>
-    <t>200005553106686078977002650080</t>
-  </si>
-  <si>
-    <t>4200003153202609099953227050</t>
-  </si>
-  <si>
-    <t>200005553105092747265161419476</t>
-  </si>
-  <si>
-    <t>4200003226202609099726208216</t>
-  </si>
-  <si>
-    <t>200005553104090044416002323338</t>
-  </si>
-  <si>
-    <t>刘丰铭 (野原新之粥)</t>
-  </si>
-  <si>
-    <t>53010003405158202609093320986772</t>
-  </si>
-  <si>
-    <t>1000050001202609090036880810018</t>
-  </si>
-  <si>
-    <t>53110002233078202609080062264290</t>
-  </si>
-  <si>
-    <t>10001073012026090801679778308500</t>
-  </si>
-  <si>
-    <t>53110002115201202609080103194589</t>
-  </si>
-  <si>
-    <t>10001073012026090801286696916557</t>
-  </si>
-  <si>
-    <t>立印</t>
-  </si>
-  <si>
-    <t>022CE4打印</t>
-  </si>
-  <si>
-    <t>4500000354202609083591200525</t>
-  </si>
-  <si>
-    <t>bbdcb9ecab8111f19cd25b5ed09b18e6</t>
-  </si>
-  <si>
-    <t>4500000383202609087985056751</t>
-  </si>
-  <si>
-    <t>980237f4ab8111f1aae9b7486e26d2ad</t>
-  </si>
-  <si>
-    <t>4200003236202609085684832972</t>
-  </si>
-  <si>
-    <t>200005553106743063552951448907</t>
-  </si>
-  <si>
-    <t>4200003242202609085379795959</t>
-  </si>
-  <si>
-    <t>200005553107565950977729615149</t>
-  </si>
-  <si>
-    <t>4200003231202609076864146230</t>
-  </si>
-  <si>
-    <t>200005553104475452417437177181</t>
-  </si>
-  <si>
-    <t>1000050001202609070031846417407</t>
-  </si>
-  <si>
-    <t>1000050001202609070732412602406</t>
-  </si>
-  <si>
-    <t>4200003236202609078795818763</t>
-  </si>
-  <si>
-    <t>200005553107368050688859192631</t>
-  </si>
-  <si>
-    <t>1000050001202609060637536845232</t>
-  </si>
-  <si>
-    <t>1000050001202609060035769426098</t>
-  </si>
-  <si>
-    <t>1000050001202609060731888992493</t>
-  </si>
-  <si>
-    <t>1000050001202609060025066146499</t>
-  </si>
-  <si>
-    <t>1000050001202609060733276312618</t>
-  </si>
-  <si>
-    <t>4200003160202609065664285985</t>
-  </si>
-  <si>
-    <t>200005553100010800129204428515</t>
-  </si>
-  <si>
-    <t>4200003244202609069254264855</t>
-  </si>
-  <si>
-    <t>200005553105651863553854582677</t>
-  </si>
-  <si>
-    <t>4200003145202609065540925197</t>
-  </si>
-  <si>
-    <t>200005553106887051265628176338</t>
-  </si>
-  <si>
-    <t>53010003386060202609062861339625</t>
-  </si>
-  <si>
-    <t>1000050001202609060530394131590</t>
-  </si>
-  <si>
-    <t>53010003367030202609063641539116</t>
-  </si>
-  <si>
-    <t>1000050001202609060335259050968</t>
-  </si>
-  <si>
-    <t>4200003149202609069364851968</t>
-  </si>
-  <si>
-    <t>200005553105880343552837475063</t>
-  </si>
-  <si>
-    <t>4500000351202609067899525988</t>
-  </si>
-  <si>
-    <t>20260906110113130266224970258824</t>
-  </si>
-  <si>
-    <t>南宁西乡塘区滔滔不绝餐饮店</t>
-  </si>
-  <si>
-    <t>南宁西乡塘区滔滔不绝餐饮店-消费</t>
-  </si>
-  <si>
-    <t>4500000325202609068430623565</t>
-  </si>
-  <si>
-    <t>1120260906000141307020</t>
-  </si>
-  <si>
-    <t>南宁市西乡塘区湘邕零食店（个体工商户）</t>
-  </si>
-  <si>
-    <t>恰货铺子南宁财经学院店</t>
-  </si>
-  <si>
-    <t>4200003230202609064192780023</t>
-  </si>
-  <si>
-    <t>7895215211993789</t>
+    <t>000000000000000000000000000000000000036</t>
+  </si>
+  <si>
+    <t>示例收款人戊</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000037</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100037</t>
+  </si>
+  <si>
+    <t>示例收款人己</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000038</t>
+  </si>
+  <si>
+    <t>00100038Nf0000000002003300030630</t>
+  </si>
+  <si>
+    <t>示例收款人庚</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000039</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100039</t>
+  </si>
+  <si>
+    <t>示例收款人辛</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000040</t>
+  </si>
+  <si>
+    <t>000000000000000000100040</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000041</t>
+  </si>
+  <si>
+    <t>示例收款人壬</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000042</t>
+  </si>
+  <si>
+    <t>XP0000000000000000000000100042</t>
+  </si>
+  <si>
+    <t>示例收款人癸</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000043</t>
+  </si>
+  <si>
+    <t>E000000000100043C16602A16647U6CF</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000044</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100044</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000045</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100045</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000046</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000100046</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000047</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100047</t>
+  </si>
+  <si>
+    <t>示例收款人甲</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000048</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100048</t>
+  </si>
+  <si>
+    <t>示例收款人乙</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000049</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100049</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000050</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100050</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000051</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100051</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000052</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100052</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000053</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100053</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000054</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100054</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000055</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100055</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000056</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100056</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000057</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100057</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000058</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100058</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000059</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100059</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000060</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100060</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000061</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000062</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100062</t>
+  </si>
+  <si>
+    <t>示例收款人丙</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000063</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100063</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000064</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100064</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000065</t>
+  </si>
+  <si>
+    <t>示例收款人丁</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000066</t>
+  </si>
+  <si>
+    <t>0000000000100066</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000067</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100067</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000068</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100068</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000069</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100069</t>
+  </si>
+  <si>
+    <t>示例收款人戊</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000070</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000100070</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000071</t>
+  </si>
+  <si>
+    <t>00000000100071U21621006009367661</t>
+  </si>
+  <si>
+    <t>示例收款人庚</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000072</t>
+  </si>
+  <si>
+    <t>0000000000000000000000100072</t>
+  </si>
+  <si>
+    <t>示例收款人己</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000073</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100073</t>
+  </si>
+  <si>
+    <t>示例收款人庚</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000074</t>
+  </si>
+  <si>
+    <t>M00000000000100074</t>
+  </si>
+  <si>
+    <t>示例收款人辛</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000075</t>
+  </si>
+  <si>
+    <t>00000000000000100075</t>
+  </si>
+  <si>
+    <t>示例收款人壬</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000076</t>
+  </si>
+  <si>
+    <t>0000000000000000100076</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000077</t>
+  </si>
+  <si>
+    <t>00000000000000100077</t>
+  </si>
+  <si>
+    <t>示例收款人癸</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000078</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100078</t>
+  </si>
+  <si>
+    <t>示例收款人甲</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000079</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100079</t>
+  </si>
+  <si>
+    <t>示例收款人乙</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000080</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100080</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000081</t>
+  </si>
+  <si>
+    <t>0000000000100081</t>
+  </si>
+  <si>
+    <t>示例收款人丙</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000082</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100082</t>
+  </si>
+  <si>
+    <t>示例收款人丁</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000083</t>
+  </si>
+  <si>
+    <t>00000000100083R2436719</t>
+  </si>
+  <si>
+    <t>示例收款人戊</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000084</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100084</t>
+  </si>
+  <si>
+    <t>示例收款人己</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000085</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100085</t>
+  </si>
+  <si>
+    <t>示例收款人庚</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000086</t>
+  </si>
+  <si>
+    <t>0000000000000000000000100086</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000087</t>
+  </si>
+  <si>
+    <t>0000000000000000000000100087</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000088</t>
+  </si>
+  <si>
+    <t>0000000000000000000000100088</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000089</t>
+  </si>
+  <si>
+    <t>0000000000000000000000100089</t>
+  </si>
+  <si>
+    <t>示例收款人辛</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000090</t>
+  </si>
+  <si>
+    <t>0000000000100090</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000091</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100091</t>
+  </si>
+  <si>
+    <t>示例收款人壬</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000092</t>
+  </si>
+  <si>
+    <t>00100092CCc7a0ff</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000093</t>
+  </si>
+  <si>
+    <t>0000000000000000000000100093</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000094</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100094</t>
+  </si>
+  <si>
+    <t>示例收款人癸</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000095</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000096</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100096</t>
+  </si>
+  <si>
+    <t>示例收款人甲</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000097</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000098</t>
+  </si>
+  <si>
+    <t>示例收款人乙</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000099</t>
+  </si>
+  <si>
+    <t>示例收款人丙</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000100</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000101</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000102</t>
+  </si>
+  <si>
+    <t>示例收款人丁</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000103</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000104</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100104</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000105</t>
+  </si>
+  <si>
+    <t>0000000000000000000100105</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000106</t>
+  </si>
+  <si>
+    <t>0000000000000000000000100106</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000107</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000100107</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000108</t>
+  </si>
+  <si>
+    <t>M00000000000100108</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000109</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100109</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000110</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100110</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000111</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100111</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000112</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100112</t>
+  </si>
+  <si>
+    <t>示例收款人戊</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000113</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100113</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000114</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100114</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000115</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100115</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000116</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100116</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000117</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100117</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000118</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000100118</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000119</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100119</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000120</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100120</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000121</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100121</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000122</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100122</t>
+  </si>
+  <si>
+    <t>示例收款人己</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000123</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000100123</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000124</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100124</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000125</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100125</t>
+  </si>
+  <si>
+    <t>示例收款人庚</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000126</t>
+  </si>
+  <si>
+    <t>bbdcb6ecab8111f19cd25b5ed09b18e6</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000127</t>
+  </si>
+  <si>
+    <t>100127f4ab8111f1aae9b7486e26d2ad</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000128</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100128</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000129</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100129</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000130</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100130</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000131</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000132</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000133</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100133</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000134</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000135</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000136</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000137</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000138</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000139</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100139</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000140</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100140</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000141</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100141</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000142</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000100142</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000143</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000100143</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000144</t>
+  </si>
+  <si>
+    <t>000000000000000000000000100144</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000145</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100145</t>
+  </si>
+  <si>
+    <t>示例收款人辛</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000146</t>
+  </si>
+  <si>
+    <t>0000000000000000100146</t>
+  </si>
+  <si>
+    <t>示例收款人壬</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000147</t>
+  </si>
+  <si>
+    <t>0000000000100147</t>
   </si>
   <si>
     <t>已存入零钱</t>
   </si>
   <si>
-    <t>1000050001202609050432846894870</t>
-  </si>
-  <si>
-    <t>1000050001202609050236992358469</t>
-  </si>
-  <si>
-    <t>4200003232202609056173304657</t>
-  </si>
-  <si>
-    <t>7895084235692838</t>
-  </si>
-  <si>
-    <t>53010003345120202609051766641394</t>
-  </si>
-  <si>
-    <t>1000050001202609050530426076575</t>
-  </si>
-  <si>
-    <t>覃记炒粉19968228439</t>
-  </si>
-  <si>
-    <t>4500000356202609055736490148</t>
-  </si>
-  <si>
-    <t>10068849260817886076400103434700</t>
-  </si>
-  <si>
-    <t>1000050001202609050130703485499</t>
-  </si>
-  <si>
-    <t>校园缴费_1020401:4600.00元</t>
-  </si>
-  <si>
-    <t>4500000319202609053140120264</t>
-  </si>
-  <si>
-    <t>gxufe26090512312992695</t>
-  </si>
-  <si>
-    <t>成都鱼庄</t>
-  </si>
-  <si>
-    <t>53110002111153202609050143990705</t>
-  </si>
-  <si>
-    <t>10001073012026090501985479501567</t>
-  </si>
-  <si>
-    <t>百色市右江区一通蔬菜</t>
-  </si>
-  <si>
-    <t>53110002261089202609051030749233</t>
-  </si>
-  <si>
-    <t>10001073012026090501825184463639</t>
-  </si>
-  <si>
-    <t>宏发医药(鼎盛店)-美团App-26090411200700001304164640594729</t>
-  </si>
-  <si>
-    <t>4500000333202609044252905430</t>
-  </si>
-  <si>
-    <t>20260904101329U67164849644707504</t>
-  </si>
-  <si>
-    <t>132100005020103202609030012220464479101</t>
-  </si>
-  <si>
-    <t>中铁网络-退款</t>
+    <t>0000000000000000000000000000148</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000149</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000150</t>
+  </si>
+  <si>
+    <t>0000000000100150</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000151</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000100151</t>
+  </si>
+  <si>
+    <t>示例收款人癸</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000152</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100152</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000153</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000154</t>
+  </si>
+  <si>
+    <t>gxufe00000000000100154</t>
+  </si>
+  <si>
+    <t>示例收款人甲</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000155</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100155</t>
+  </si>
+  <si>
+    <t>示例收款人乙</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000156</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100156</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000157</t>
+  </si>
+  <si>
+    <t>00000000100157U67164849644707504</t>
+  </si>
+  <si>
+    <t>000000000000000000000000000000000000158</t>
+  </si>
+  <si>
+    <t>示例收款人庚-退款</t>
   </si>
   <si>
     <t>已退款¥78.50</t>
   </si>
   <si>
-    <t>50302008622026090362929383939</t>
-  </si>
-  <si>
-    <t>53110002268073202609033709158998</t>
-  </si>
-  <si>
-    <t>10001073012026090301599672163509</t>
-  </si>
-  <si>
-    <t>4500000345202609039867724111</t>
-  </si>
-  <si>
-    <t>20260903Nf0000000006000870149010</t>
+    <t>00000000000000000000000000159</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000160</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100160</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000161</t>
+  </si>
+  <si>
+    <t>00100161Nf0000000006000870149010</t>
   </si>
   <si>
     <t>对方已退还</t>
   </si>
   <si>
-    <t>53010003396205202609032597857265</t>
-  </si>
-  <si>
-    <t>1000050001202609030631595402198</t>
-  </si>
-  <si>
-    <t>京东-订单编号3610420018284160</t>
-  </si>
-  <si>
-    <t>4500000342202609032433111453</t>
-  </si>
-  <si>
-    <t>1012731226090311513301711</t>
-  </si>
-  <si>
-    <t>川贵特产</t>
-  </si>
-  <si>
-    <t>商户收款</t>
-  </si>
-  <si>
-    <t>4500000360202609028937348754</t>
-  </si>
-  <si>
-    <t>30258489833731173340363988194904</t>
-  </si>
-  <si>
-    <t>彬</t>
-  </si>
-  <si>
-    <t>53110002238249202609020228658514</t>
-  </si>
-  <si>
-    <t>10001073012026090201206342255606</t>
-  </si>
-  <si>
-    <t>4500000372202609027244229503</t>
-  </si>
-  <si>
-    <t>10068822733617883404320188189400</t>
-  </si>
-  <si>
-    <t>4500000335202609025679285856</t>
-  </si>
-  <si>
-    <t>10068822749217883403480117325900</t>
-  </si>
-  <si>
-    <t>53110002232129202609020679517804</t>
-  </si>
-  <si>
-    <t>10001073012026090201517664779593</t>
-  </si>
-  <si>
-    <t>夸克</t>
-  </si>
-  <si>
-    <t>连续包月(夸克网盘SVIP会员)</t>
-  </si>
-  <si>
-    <t>4500000384202609028347229623</t>
-  </si>
-  <si>
-    <t>573770469260093199</t>
-  </si>
-  <si>
-    <t>福州街冰淇淋批发部</t>
-  </si>
-  <si>
-    <t>53110002267051202609013549535473</t>
-  </si>
-  <si>
-    <t>10001073012026090101220696201576</t>
-  </si>
-  <si>
-    <t>蜂蜜小面包丨店</t>
-  </si>
-  <si>
-    <t>53110002281032202608313519822098</t>
-  </si>
-  <si>
-    <t>10001073012026083101578933007600</t>
-  </si>
-  <si>
-    <t>53010003399106202608311942643530</t>
-  </si>
-  <si>
-    <t>1000050001202608310030681732456</t>
-  </si>
-  <si>
-    <t>1000050001202608310637855514166</t>
-  </si>
-  <si>
-    <t>蜜雪冰城股份有限公司-退款</t>
-  </si>
-  <si>
-    <t>蜜雪冰城股份有限公司</t>
-  </si>
-  <si>
-    <t>50300508602026083054714504489</t>
-  </si>
-  <si>
-    <t>4500000334202608303383567325</t>
-  </si>
-  <si>
-    <t>2001052608300104875058244370</t>
-  </si>
-  <si>
-    <t>笔记本清灰-更换硅脂</t>
-  </si>
-  <si>
-    <t>4500000351202608309218527454</t>
-  </si>
-  <si>
-    <t>2001052608300104912863806999</t>
+    <t>00000000000000000000000000000162</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000100162</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000163</t>
+  </si>
+  <si>
+    <t>0000000000000000000100163</t>
+  </si>
+  <si>
+    <t>示例收款人丙</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000164</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100164</t>
+  </si>
+  <si>
+    <t>示例收款人丁</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000165</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100165</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000166</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100166</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000167</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100167</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000168</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100168</t>
+  </si>
+  <si>
+    <t>示例收款人戊</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000169</t>
+  </si>
+  <si>
+    <t>000000000000100169</t>
+  </si>
+  <si>
+    <t>示例收款人己</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000170</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100170</t>
+  </si>
+  <si>
+    <t>示例收款人庚</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000171</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100171</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000172</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000100172</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000173</t>
+  </si>
+  <si>
+    <t>示例收款人辛-退款</t>
+  </si>
+  <si>
+    <t>示例收款人辛</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000174</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000175</t>
+  </si>
+  <si>
+    <t>0000000000000000000000100175</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000176</t>
+  </si>
+  <si>
+    <t>0000000000000000000000100176</t>
   </si>
   <si>
     <t>已退款(¥78.50)</t>
   </si>
   <si>
-    <t>4500000346202608291705294700</t>
-  </si>
-  <si>
-    <t>M20260829222689724</t>
-  </si>
-  <si>
-    <t>1000050001202608290237927426114</t>
-  </si>
-  <si>
-    <t>53010003367220202608292732054073</t>
-  </si>
-  <si>
-    <t>1000050001202608290138534158765</t>
-  </si>
-  <si>
-    <t>德保山黄牛</t>
-  </si>
-  <si>
-    <t>4500000383202608293169910164</t>
-  </si>
-  <si>
-    <t>10068787705217879714280123535501</t>
-  </si>
-  <si>
-    <t>香辣串串</t>
-  </si>
-  <si>
-    <t>53110002134165202608291462435225</t>
-  </si>
-  <si>
-    <t>10001073012026082901360323021580</t>
-  </si>
-  <si>
-    <t>4500000360202608292377650645</t>
-  </si>
-  <si>
-    <t>10068787638017879710120157049200</t>
-  </si>
-  <si>
-    <t>4200003241202608283191423681</t>
-  </si>
-  <si>
-    <t>83620260828756025458</t>
-  </si>
-  <si>
-    <t>京东-订单编号3604420001513468</t>
-  </si>
-  <si>
-    <t>4500000319202608281985912043</t>
-  </si>
-  <si>
-    <t>1012736026082812573903684</t>
+    <t>0000000000000000000000000177</t>
+  </si>
+  <si>
+    <t>M00000000000100177</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000000178</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000179</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000100179</t>
+  </si>
+  <si>
+    <t>示例收款人壬</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000180</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100180</t>
+  </si>
+  <si>
+    <t>示例收款人癸</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000000181</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100181</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000182</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000100182</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000183</t>
+  </si>
+  <si>
+    <t>00000000000000100183</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>0000000000000000000000000184</t>
+  </si>
+  <si>
+    <t>0000000000000000000100184</t>
   </si>
 </sst>
 </file>
@@ -4381,8 +4381,10 @@
       <c r="C92" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D92" s="2" t="s">
-        <v>242</v>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>示例商品</t>
+        </is>
       </c>
       <c r="E92" s="2" t="s">
         <v>29</v>
@@ -6724,8 +6726,10 @@
       <c r="C159" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D159" s="2" t="s">
-        <v>188</v>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>示例商品</t>
+        </is>
       </c>
       <c r="E159" s="2" t="s">
         <v>50</v>
@@ -7247,8 +7251,10 @@
       <c r="C174" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="D174" s="2" t="s">
-        <v>420</v>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>示例商品</t>
+        </is>
       </c>
       <c r="E174" s="2" t="s">
         <v>50</v>
